--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N62_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N62_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.85084969855331</v>
+        <v>3.063263076014913</v>
       </c>
       <c r="D2" t="n">
-        <v>17.89073048135424</v>
+        <v>2.907243703220065</v>
       </c>
       <c r="E2" t="n">
-        <v>23.88970416188481</v>
+        <v>3.882076926306282</v>
       </c>
       <c r="F2" t="n">
-        <v>11.42122978002389</v>
+        <v>1.855949839253883</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.87967704014952</v>
+        <v>3.717947519024297</v>
       </c>
       <c r="D3" t="n">
-        <v>15.28030282163896</v>
+        <v>2.483049208516332</v>
       </c>
       <c r="E3" t="n">
-        <v>23.88970416188481</v>
+        <v>3.882076926306282</v>
       </c>
       <c r="F3" t="n">
-        <v>11.42122978002389</v>
+        <v>1.855949839253883</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>62.10658098671593</v>
+        <v>10.09231941034134</v>
       </c>
       <c r="D4" t="n">
-        <v>31.50253972591316</v>
+        <v>5.119162705460888</v>
       </c>
       <c r="E4" t="n">
-        <v>23.88970416188481</v>
+        <v>3.882076926306282</v>
       </c>
       <c r="F4" t="n">
-        <v>11.42122978002389</v>
+        <v>1.855949839253883</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>76.38255209564579</v>
+        <v>12.41216471554244</v>
       </c>
       <c r="D5" t="n">
-        <v>46.77471874460926</v>
+        <v>7.600891795999005</v>
       </c>
       <c r="E5" t="n">
-        <v>23.88970416188481</v>
+        <v>3.882076926306282</v>
       </c>
       <c r="F5" t="n">
-        <v>11.42122978002389</v>
+        <v>1.855949839253883</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>22.61010907243441</v>
+        <v>3.674142724270591</v>
       </c>
       <c r="D6" t="n">
-        <v>22.43613190152869</v>
+        <v>3.645871433998413</v>
       </c>
       <c r="E6" t="n">
-        <v>23.88970416188481</v>
+        <v>3.882076926306282</v>
       </c>
       <c r="F6" t="n">
-        <v>11.42122978002389</v>
+        <v>1.855949839253883</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
